--- a/grupos/5BEM - Estadisticos 20211.xlsx
+++ b/grupos/5BEM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="141">
   <si>
     <t>Materia</t>
   </si>
@@ -185,18 +185,18 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
+    <t>Cruz Alejo José Armando</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
-  </si>
-  <si>
-    <t>Cruz Alejo José Armando</t>
-  </si>
-  <si>
     <t>Aurioles Maldonado Luis Gustavo</t>
   </si>
   <si>
@@ -212,103 +212,190 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>CITLAHUA</t>
+  </si>
+  <si>
+    <t>CONDADO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TOCOHUA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GARATE</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ANTEMATE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>ELEAZAR RIGOBERTO</t>
+  </si>
+  <si>
+    <t>RAUL ARTURO</t>
+  </si>
+  <si>
+    <t>JOSUE ALEXIS</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>JUAN ANTONIO</t>
+  </si>
+  <si>
+    <t>ADRIANA</t>
+  </si>
+  <si>
+    <t>AXEL MIGUEL</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>JOSE ALONSO</t>
+  </si>
+  <si>
+    <t>ROMARIO ALDAIR</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>ADOLFO</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>CITLAHUA</t>
-  </si>
-  <si>
-    <t>CONDADO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MORALES</t>
+    <t>CADEZA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>FLORENCIO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
   </si>
   <si>
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>ROJAS</t>
+    <t>OCTAVIANO</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
     <t>TAPIA</t>
   </si>
   <si>
-    <t>TOCOHUA</t>
-  </si>
-  <si>
     <t>TEXOCO</t>
   </si>
   <si>
     <t>TEZOCO</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GARATE</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ANTEMATE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DEL ANGEL</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>ANGUIANO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>BERISTAIN</t>
+    <t>TETLA</t>
   </si>
   <si>
     <t>JOSE JAZAEL</t>
@@ -317,40 +404,31 @@
     <t>JOSE ANTONIO</t>
   </si>
   <si>
-    <t>ELEAZAR RIGOBERTO</t>
-  </si>
-  <si>
-    <t>RAUL ARTURO</t>
-  </si>
-  <si>
-    <t>JOSUE ALEXIS</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>JAFET</t>
-  </si>
-  <si>
-    <t>JUAN ANTONIO</t>
-  </si>
-  <si>
-    <t>ADRIANA</t>
-  </si>
-  <si>
-    <t>AXEL MIGUEL</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>AXEL</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>JOSE ALONSO</t>
+    <t>IRVING OTTONIEL</t>
+  </si>
+  <si>
+    <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>JUAN LUIS</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>OSWALDO ENRIQUE</t>
+  </si>
+  <si>
+    <t>YAEL</t>
   </si>
   <si>
     <t>ARIAN ALEXIS</t>
@@ -359,85 +437,7 @@
     <t>YARITZI</t>
   </si>
   <si>
-    <t>ROMARIO ALDAIR</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
     <t>MARIA ISABEL</t>
-  </si>
-  <si>
-    <t>ADOLFO</t>
-  </si>
-  <si>
-    <t>CADEZA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>FLORENCIO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OCTAVIANO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DEL ANGEL</t>
-  </si>
-  <si>
-    <t>MIRON</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>IRVING OTTONIEL</t>
-  </si>
-  <si>
-    <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
-  </si>
-  <si>
-    <t>JESUS ENRIQUE</t>
-  </si>
-  <si>
-    <t>JUAN LUIS</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>OSWALDO ENRIQUE</t>
-  </si>
-  <si>
-    <t>YAEL</t>
   </si>
   <si>
     <t>JOSUE GILBERTO</t>
@@ -954,34 +954,34 @@
         <v>9</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1011,19 +1011,19 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z4">
         <v>9</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB4">
         <v>10</v>
       </c>
       <c r="AC4">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1037,7 +1037,7 @@
         <v>8</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>5</v>
@@ -1052,25 +1052,25 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1094,13 +1094,13 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z5">
         <v>5</v>
@@ -1141,25 +1141,25 @@
         <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1186,7 +1186,7 @@
         <v>10</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1230,25 +1230,25 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1319,25 +1319,25 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1367,7 +1367,7 @@
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z8">
         <v>9</v>
@@ -1390,10 +1390,10 @@
         <v>-1</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E9">
         <v>-1</v>
@@ -1405,28 +1405,28 @@
         <v>-1</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N9">
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1453,22 +1453,22 @@
         <v>-1</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z9">
         <v>-1</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB9">
         <v>-1</v>
       </c>
       <c r="AC9">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1479,10 +1479,10 @@
         <v>7</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E10">
         <v>-1</v>
@@ -1497,25 +1497,25 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1539,13 +1539,13 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>-1</v>
@@ -1589,22 +1589,22 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1634,7 +1634,7 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z11">
         <v>5</v>
@@ -1654,46 +1654,46 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <v>5</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G12">
         <v>-1</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1717,25 +1717,25 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z12">
         <v>5</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB12">
         <v>-1</v>
       </c>
       <c r="AC12">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1743,46 +1743,46 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C13">
         <v>7</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E13">
         <v>5</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G13">
         <v>-1</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1806,25 +1806,25 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X13">
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z13">
         <v>5</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB13">
         <v>-1</v>
       </c>
       <c r="AC13">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1853,25 +1853,25 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1895,13 +1895,13 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>9</v>
@@ -1924,43 +1924,43 @@
         <v>-1</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E15">
         <v>-1</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G15">
         <v>-1</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1987,22 +1987,22 @@
         <v>-1</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z15">
         <v>-1</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB15">
         <v>-1</v>
       </c>
       <c r="AC15">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2010,10 +2010,10 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>8</v>
@@ -2031,25 +2031,25 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2073,13 +2073,13 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z16">
         <v>6</v>
@@ -2120,25 +2120,25 @@
         <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2162,10 +2162,10 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>9</v>
@@ -2188,13 +2188,13 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C18">
         <v>6</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E18">
         <v>5</v>
@@ -2209,25 +2209,25 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2251,13 +2251,13 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z18">
         <v>5</v>
@@ -2298,25 +2298,25 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2340,13 +2340,13 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>6</v>
@@ -2387,25 +2387,25 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2429,7 +2429,7 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>6</v>
@@ -2455,10 +2455,10 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>7</v>
@@ -2476,25 +2476,25 @@
         <v>9</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2518,10 +2518,10 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2565,25 +2565,25 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2613,7 +2613,7 @@
         <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z22">
         <v>10</v>
@@ -2654,25 +2654,25 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2696,13 +2696,13 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z23">
         <v>8</v>
@@ -2725,43 +2725,43 @@
         <v>-1</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E24">
         <v>-1</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G24">
         <v>-1</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I24">
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2788,22 +2788,22 @@
         <v>-1</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z24">
         <v>-1</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB24">
         <v>-1</v>
       </c>
       <c r="AC24">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2832,25 +2832,25 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2880,19 +2880,19 @@
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z25">
         <v>8</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB25">
         <v>7</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2906,7 +2906,7 @@
         <v>6</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E26">
         <v>5</v>
@@ -2924,22 +2924,22 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2969,7 +2969,7 @@
         <v>6</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z26">
         <v>5</v>
@@ -2989,46 +2989,46 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E27">
         <v>5</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G27">
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3052,25 +3052,25 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z27">
         <v>5</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB27">
         <v>7</v>
       </c>
       <c r="AC27">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3099,25 +3099,25 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3144,7 +3144,7 @@
         <v>7</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -3179,34 +3179,34 @@
         <v>6</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G29">
         <v>-1</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N29">
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3230,25 +3230,25 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z29">
         <v>6</v>
       </c>
       <c r="AA29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB29">
         <v>-1</v>
       </c>
       <c r="AC29">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3268,34 +3268,34 @@
         <v>8</v>
       </c>
       <c r="F30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G30">
         <v>7</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -3319,10 +3319,10 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>9</v>
@@ -3331,13 +3331,13 @@
         <v>8</v>
       </c>
       <c r="AA30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB30">
         <v>7</v>
       </c>
       <c r="AC30">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3345,10 +3345,10 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D31">
         <v>7</v>
@@ -3366,25 +3366,25 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3408,10 +3408,10 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y31">
         <v>7</v>
@@ -3434,10 +3434,10 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D32">
         <v>7</v>
@@ -3455,25 +3455,25 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3497,10 +3497,10 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y32">
         <v>7</v>
@@ -3526,7 +3526,7 @@
         <v>6</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>9</v>
@@ -3544,25 +3544,25 @@
         <v>8</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3586,10 +3586,10 @@
         <v>-1</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y33">
         <v>9</v>
@@ -3633,25 +3633,25 @@
         <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3678,10 +3678,10 @@
         <v>10</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z34">
         <v>9</v>
@@ -3713,34 +3713,34 @@
         <v>7</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G35">
         <v>-1</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3767,7 +3767,7 @@
         <v>6</v>
       </c>
       <c r="X35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y35">
         <v>6</v>
@@ -3776,13 +3776,13 @@
         <v>7</v>
       </c>
       <c r="AA35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB35">
         <v>-1</v>
       </c>
       <c r="AC35">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3870,7 +3870,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3879,30 +3879,30 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>59.38</v>
+        <v>62.5</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>40.63</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3911,30 +3911,30 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4">
-        <v>62.5</v>
+        <v>68.75</v>
       </c>
       <c r="G4">
-        <v>25</v>
+        <v>31.25</v>
       </c>
       <c r="H4">
         <v>6.9</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>12.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3943,30 +3943,30 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>78.13</v>
+      </c>
+      <c r="G5">
+        <v>21.88</v>
+      </c>
+      <c r="H5">
+        <v>7.1</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>65.63</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>7.6</v>
-      </c>
-      <c r="I5">
-        <v>11</v>
-      </c>
-      <c r="J5">
-        <v>34.38</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -3975,13 +3975,13 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>68.75</v>
+        <v>84.38</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -3990,15 +3990,15 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>31.25</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -4007,30 +4007,30 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>31.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>59</v>
@@ -4039,25 +4039,25 @@
         <v>32</v>
       </c>
       <c r="D8">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>71.88</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>9.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>28.13</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4067,7 +4067,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4096,139 +4096,139 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>19330051920085</v>
+        <v>19330051920092</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920084</v>
+        <v>19330051920092</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920084</v>
+        <v>19330051920091</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920092</v>
+        <v>19330051920091</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920092</v>
+        <v>19330051920091</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920092</v>
+        <v>19330051920093</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920092</v>
+        <v>19330051920093</v>
       </c>
       <c r="B8" t="s">
         <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>58</v>
@@ -4236,16 +4236,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920091</v>
+        <v>19330051920094</v>
       </c>
       <c r="B9" t="s">
         <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -4256,116 +4256,116 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920091</v>
+        <v>19330051920095</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920091</v>
+        <v>19330051920098</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920091</v>
+        <v>19330051920098</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920091</v>
+        <v>19330051920098</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920091</v>
+        <v>19330051920099</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920093</v>
+        <v>19330051920101</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -4376,36 +4376,36 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920093</v>
+        <v>19330051920102</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920094</v>
+        <v>19330051920105</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -4416,116 +4416,116 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920094</v>
+        <v>19330051920109</v>
       </c>
       <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s">
         <v>69</v>
       </c>
-      <c r="C18" t="s">
-        <v>87</v>
-      </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920094</v>
+        <v>19330051920109</v>
       </c>
       <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s">
         <v>69</v>
       </c>
-      <c r="C19" t="s">
-        <v>87</v>
-      </c>
       <c r="D19" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920094</v>
+        <v>19330051920109</v>
       </c>
       <c r="B20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" t="s">
         <v>69</v>
       </c>
-      <c r="C20" t="s">
-        <v>87</v>
-      </c>
       <c r="D20" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920094</v>
+        <v>19330051920112</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920094</v>
+        <v>19330051920112</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E22" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920095</v>
+        <v>19330051920116</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D23" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -4536,1022 +4536,62 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920095</v>
+        <v>19330051920118</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>19330051920095</v>
+        <v>19330051920119</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920095</v>
+        <v>19330051920122</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="D26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920095</v>
-      </c>
-      <c r="B27" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" t="s">
-        <v>103</v>
-      </c>
-      <c r="E27" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051920098</v>
-      </c>
-      <c r="B28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" t="s">
-        <v>104</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>19330051920098</v>
-      </c>
-      <c r="B29" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" t="s">
-        <v>104</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>19330051920098</v>
-      </c>
-      <c r="B30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" t="s">
-        <v>104</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>19330051920098</v>
-      </c>
-      <c r="B31" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" t="s">
-        <v>70</v>
-      </c>
-      <c r="D31" t="s">
-        <v>104</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>19330051920098</v>
-      </c>
-      <c r="B32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" t="s">
-        <v>70</v>
-      </c>
-      <c r="D32" t="s">
-        <v>104</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>19330051920098</v>
-      </c>
-      <c r="B33" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" t="s">
-        <v>104</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>19330051920098</v>
-      </c>
-      <c r="B34" t="s">
-        <v>71</v>
-      </c>
-      <c r="C34" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" t="s">
-        <v>104</v>
-      </c>
-      <c r="E34" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>19330051920099</v>
-      </c>
-      <c r="B35" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" t="s">
-        <v>88</v>
-      </c>
-      <c r="D35" t="s">
-        <v>105</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>19330051920099</v>
-      </c>
-      <c r="B36" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" t="s">
-        <v>88</v>
-      </c>
-      <c r="D36" t="s">
-        <v>105</v>
-      </c>
-      <c r="E36" t="s">
-        <v>5</v>
-      </c>
-      <c r="F36" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330051920099</v>
-      </c>
-      <c r="B37" t="s">
-        <v>71</v>
-      </c>
-      <c r="C37" t="s">
-        <v>88</v>
-      </c>
-      <c r="D37" t="s">
-        <v>105</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>19330051920101</v>
-      </c>
-      <c r="B38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" t="s">
-        <v>89</v>
-      </c>
-      <c r="D38" t="s">
-        <v>106</v>
-      </c>
-      <c r="E38" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>19330051920101</v>
-      </c>
-      <c r="B39" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" t="s">
-        <v>89</v>
-      </c>
-      <c r="D39" t="s">
-        <v>106</v>
-      </c>
-      <c r="E39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>19330051920101</v>
-      </c>
-      <c r="B40" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40" t="s">
-        <v>89</v>
-      </c>
-      <c r="D40" t="s">
-        <v>106</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>19330051920102</v>
-      </c>
-      <c r="B41" t="s">
-        <v>72</v>
-      </c>
-      <c r="C41" t="s">
-        <v>90</v>
-      </c>
-      <c r="D41" t="s">
-        <v>107</v>
-      </c>
-      <c r="E41" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>19330051920105</v>
-      </c>
-      <c r="B42" t="s">
-        <v>73</v>
-      </c>
-      <c r="C42" t="s">
-        <v>91</v>
-      </c>
-      <c r="D42" t="s">
-        <v>108</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>19330051920105</v>
-      </c>
-      <c r="B43" t="s">
-        <v>73</v>
-      </c>
-      <c r="C43" t="s">
-        <v>91</v>
-      </c>
-      <c r="D43" t="s">
-        <v>108</v>
-      </c>
-      <c r="E43" t="s">
-        <v>5</v>
-      </c>
-      <c r="F43" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>19330051920105</v>
-      </c>
-      <c r="B44" t="s">
-        <v>73</v>
-      </c>
-      <c r="C44" t="s">
-        <v>91</v>
-      </c>
-      <c r="D44" t="s">
-        <v>108</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920109</v>
-      </c>
-      <c r="B45" t="s">
-        <v>74</v>
-      </c>
-      <c r="C45" t="s">
-        <v>71</v>
-      </c>
-      <c r="D45" t="s">
-        <v>109</v>
-      </c>
-      <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>19330051920109</v>
-      </c>
-      <c r="B46" t="s">
-        <v>74</v>
-      </c>
-      <c r="C46" t="s">
-        <v>71</v>
-      </c>
-      <c r="D46" t="s">
-        <v>109</v>
-      </c>
-      <c r="E46" t="s">
-        <v>5</v>
-      </c>
-      <c r="F46" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>19330051920109</v>
-      </c>
-      <c r="B47" t="s">
-        <v>74</v>
-      </c>
-      <c r="C47" t="s">
-        <v>71</v>
-      </c>
-      <c r="D47" t="s">
-        <v>109</v>
-      </c>
-      <c r="E47" t="s">
-        <v>6</v>
-      </c>
-      <c r="F47" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>19330051920109</v>
-      </c>
-      <c r="B48" t="s">
-        <v>74</v>
-      </c>
-      <c r="C48" t="s">
-        <v>71</v>
-      </c>
-      <c r="D48" t="s">
-        <v>109</v>
-      </c>
-      <c r="E48" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>19330051920109</v>
-      </c>
-      <c r="B49" t="s">
-        <v>74</v>
-      </c>
-      <c r="C49" t="s">
-        <v>71</v>
-      </c>
-      <c r="D49" t="s">
-        <v>109</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>19330051920109</v>
-      </c>
-      <c r="B50" t="s">
-        <v>74</v>
-      </c>
-      <c r="C50" t="s">
-        <v>71</v>
-      </c>
-      <c r="D50" t="s">
-        <v>109</v>
-      </c>
-      <c r="E50" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>19330051920109</v>
-      </c>
-      <c r="B51" t="s">
-        <v>74</v>
-      </c>
-      <c r="C51" t="s">
-        <v>71</v>
-      </c>
-      <c r="D51" t="s">
-        <v>109</v>
-      </c>
-      <c r="E51" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>19330051920112</v>
-      </c>
-      <c r="B52" t="s">
-        <v>75</v>
-      </c>
-      <c r="C52" t="s">
-        <v>70</v>
-      </c>
-      <c r="D52" t="s">
-        <v>110</v>
-      </c>
-      <c r="E52" t="s">
-        <v>10</v>
-      </c>
-      <c r="F52" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>19330051920112</v>
-      </c>
-      <c r="B53" t="s">
-        <v>75</v>
-      </c>
-      <c r="C53" t="s">
-        <v>70</v>
-      </c>
-      <c r="D53" t="s">
-        <v>110</v>
-      </c>
-      <c r="E53" t="s">
-        <v>5</v>
-      </c>
-      <c r="F53" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>19330051920112</v>
-      </c>
-      <c r="B54" t="s">
-        <v>75</v>
-      </c>
-      <c r="C54" t="s">
-        <v>70</v>
-      </c>
-      <c r="D54" t="s">
-        <v>110</v>
-      </c>
-      <c r="E54" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>19330051920001</v>
-      </c>
-      <c r="B55" t="s">
-        <v>76</v>
-      </c>
-      <c r="C55" t="s">
-        <v>92</v>
-      </c>
-      <c r="D55" t="s">
-        <v>111</v>
-      </c>
-      <c r="E55" t="s">
-        <v>5</v>
-      </c>
-      <c r="F55" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>19330051920001</v>
-      </c>
-      <c r="B56" t="s">
-        <v>76</v>
-      </c>
-      <c r="C56" t="s">
-        <v>92</v>
-      </c>
-      <c r="D56" t="s">
-        <v>111</v>
-      </c>
-      <c r="E56" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>19330051920001</v>
-      </c>
-      <c r="B57" t="s">
-        <v>76</v>
-      </c>
-      <c r="C57" t="s">
-        <v>92</v>
-      </c>
-      <c r="D57" t="s">
-        <v>111</v>
-      </c>
-      <c r="E57" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>19330051920001</v>
-      </c>
-      <c r="B58" t="s">
-        <v>76</v>
-      </c>
-      <c r="C58" t="s">
-        <v>92</v>
-      </c>
-      <c r="D58" t="s">
-        <v>111</v>
-      </c>
-      <c r="E58" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>19330051920001</v>
-      </c>
-      <c r="B59" t="s">
-        <v>76</v>
-      </c>
-      <c r="C59" t="s">
-        <v>92</v>
-      </c>
-      <c r="D59" t="s">
-        <v>111</v>
-      </c>
-      <c r="E59" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>19330051920116</v>
-      </c>
-      <c r="B60" t="s">
-        <v>77</v>
-      </c>
-      <c r="C60" t="s">
-        <v>93</v>
-      </c>
-      <c r="D60" t="s">
-        <v>102</v>
-      </c>
-      <c r="E60" t="s">
-        <v>10</v>
-      </c>
-      <c r="F60" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>19330051920116</v>
-      </c>
-      <c r="B61" t="s">
-        <v>77</v>
-      </c>
-      <c r="C61" t="s">
-        <v>93</v>
-      </c>
-      <c r="D61" t="s">
-        <v>102</v>
-      </c>
-      <c r="E61" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>19330051920116</v>
-      </c>
-      <c r="B62" t="s">
-        <v>77</v>
-      </c>
-      <c r="C62" t="s">
-        <v>93</v>
-      </c>
-      <c r="D62" t="s">
-        <v>102</v>
-      </c>
-      <c r="E62" t="s">
-        <v>11</v>
-      </c>
-      <c r="F62" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>19330051920117</v>
-      </c>
-      <c r="B63" t="s">
-        <v>78</v>
-      </c>
-      <c r="C63" t="s">
-        <v>69</v>
-      </c>
-      <c r="D63" t="s">
-        <v>112</v>
-      </c>
-      <c r="E63" t="s">
-        <v>9</v>
-      </c>
-      <c r="F63" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>19330051920117</v>
-      </c>
-      <c r="B64" t="s">
-        <v>78</v>
-      </c>
-      <c r="C64" t="s">
-        <v>69</v>
-      </c>
-      <c r="D64" t="s">
-        <v>112</v>
-      </c>
-      <c r="E64" t="s">
-        <v>11</v>
-      </c>
-      <c r="F64" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>19330051920118</v>
-      </c>
-      <c r="B65" t="s">
-        <v>79</v>
-      </c>
-      <c r="C65" t="s">
-        <v>86</v>
-      </c>
-      <c r="D65" t="s">
-        <v>113</v>
-      </c>
-      <c r="E65" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>19330051920118</v>
-      </c>
-      <c r="B66" t="s">
-        <v>79</v>
-      </c>
-      <c r="C66" t="s">
-        <v>86</v>
-      </c>
-      <c r="D66" t="s">
-        <v>113</v>
-      </c>
-      <c r="E66" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>19330051920118</v>
-      </c>
-      <c r="B67" t="s">
-        <v>79</v>
-      </c>
-      <c r="C67" t="s">
-        <v>86</v>
-      </c>
-      <c r="D67" t="s">
-        <v>113</v>
-      </c>
-      <c r="E67" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>19330051920119</v>
-      </c>
-      <c r="B68" t="s">
-        <v>80</v>
-      </c>
-      <c r="C68" t="s">
-        <v>94</v>
-      </c>
-      <c r="D68" t="s">
-        <v>114</v>
-      </c>
-      <c r="E68" t="s">
-        <v>10</v>
-      </c>
-      <c r="F68" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>19330051920119</v>
-      </c>
-      <c r="B69" t="s">
-        <v>80</v>
-      </c>
-      <c r="C69" t="s">
-        <v>94</v>
-      </c>
-      <c r="D69" t="s">
-        <v>114</v>
-      </c>
-      <c r="E69" t="s">
-        <v>5</v>
-      </c>
-      <c r="F69" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>19330051920119</v>
-      </c>
-      <c r="B70" t="s">
-        <v>80</v>
-      </c>
-      <c r="C70" t="s">
-        <v>94</v>
-      </c>
-      <c r="D70" t="s">
-        <v>114</v>
-      </c>
-      <c r="E70" t="s">
-        <v>6</v>
-      </c>
-      <c r="F70" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>19330051920120</v>
-      </c>
-      <c r="B71" t="s">
-        <v>81</v>
-      </c>
-      <c r="C71" t="s">
-        <v>95</v>
-      </c>
-      <c r="D71" t="s">
-        <v>115</v>
-      </c>
-      <c r="E71" t="s">
-        <v>6</v>
-      </c>
-      <c r="F71" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>19330051920122</v>
-      </c>
-      <c r="B72" t="s">
-        <v>82</v>
-      </c>
-      <c r="C72" t="s">
-        <v>96</v>
-      </c>
-      <c r="D72" t="s">
-        <v>116</v>
-      </c>
-      <c r="E72" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>19330051920122</v>
-      </c>
-      <c r="B73" t="s">
-        <v>82</v>
-      </c>
-      <c r="C73" t="s">
-        <v>96</v>
-      </c>
-      <c r="D73" t="s">
-        <v>116</v>
-      </c>
-      <c r="E73" t="s">
-        <v>9</v>
-      </c>
-      <c r="F73" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>19330051920122</v>
-      </c>
-      <c r="B74" t="s">
-        <v>82</v>
-      </c>
-      <c r="C74" t="s">
-        <v>96</v>
-      </c>
-      <c r="D74" t="s">
-        <v>116</v>
-      </c>
-      <c r="E74" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -5587,370 +4627,370 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920098</v>
+        <v>19330051920091</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920109</v>
+        <v>19330051920098</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920091</v>
+        <v>19330051920109</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920094</v>
+        <v>19330051920092</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920095</v>
+        <v>19330051920093</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920001</v>
+        <v>19330051920112</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920092</v>
+        <v>19330051920094</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920099</v>
+        <v>19330051920095</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920101</v>
+        <v>19330051920099</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920105</v>
+        <v>19330051920101</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920112</v>
+        <v>19330051920102</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920116</v>
+        <v>19330051920105</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920118</v>
+        <v>19330051920116</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920119</v>
+        <v>19330051920118</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920122</v>
+        <v>19330051920119</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920084</v>
+        <v>19330051920122</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920093</v>
+        <v>19330051920085</v>
       </c>
       <c r="B18" t="s">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920117</v>
+        <v>19330051920084</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920085</v>
+        <v>19330051920088</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="D20" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920102</v>
+        <v>19330051920090</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920120</v>
+        <v>19330051920089</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920088</v>
+        <v>19330051920097</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C23" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
         <v>131</v>
@@ -5961,13 +5001,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920090</v>
+        <v>19330051920100</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="D24" t="s">
         <v>132</v>
@@ -5978,13 +5018,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920089</v>
+        <v>19330051920103</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="D25" t="s">
         <v>133</v>
@@ -5995,13 +5035,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920097</v>
+        <v>19330051920106</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="C26" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s">
         <v>134</v>
@@ -6012,13 +5052,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920100</v>
+        <v>19330051920107</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s">
-        <v>126</v>
+        <v>68</v>
       </c>
       <c r="D27" t="s">
         <v>135</v>
@@ -6029,13 +5069,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920103</v>
+        <v>19330051920110</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
         <v>136</v>
@@ -6046,13 +5086,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920106</v>
+        <v>19330051920001</v>
       </c>
       <c r="B29" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D29" t="s">
         <v>137</v>
@@ -6063,16 +5103,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920107</v>
+        <v>19330051920115</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -6080,16 +5120,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920110</v>
+        <v>19330051920117</v>
       </c>
       <c r="B31" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C31" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="D31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -6097,16 +5137,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920115</v>
+        <v>19330051920120</v>
       </c>
       <c r="B32" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -6117,10 +5157,10 @@
         <v>19330051920121</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
         <v>140</v>
@@ -6136,7 +5176,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6168,22 +5208,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920085</v>
+        <v>19330051920092</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -6191,68 +5231,68 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920085</v>
+        <v>19330051920092</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920084</v>
+        <v>19330051920095</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920084</v>
+        <v>19330051920095</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -6260,45 +5300,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920117</v>
+        <v>19330051920099</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920117</v>
+        <v>19330051920099</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -6306,47 +5346,208 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920102</v>
+        <v>19330051920118</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
+        <v>19330051920118</v>
+      </c>
+      <c r="B9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>19330051920119</v>
+      </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>19330051920119</v>
+      </c>
+      <c r="B11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>19330051920085</v>
+      </c>
+      <c r="B12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920102</v>
+      </c>
+      <c r="B13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920116</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
         <v>19330051920120</v>
       </c>
-      <c r="B9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" t="s">
-        <v>115</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9">
+      <c r="B15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C15" t="s">
+        <v>124</v>
+      </c>
+      <c r="D15" t="s">
+        <v>139</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>19330051920122</v>
+      </c>
+      <c r="B16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/5BEM - Estadisticos 20211.xlsx
+++ b/grupos/5BEM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="141">
   <si>
     <t>Materia</t>
   </si>
@@ -248,199 +248,199 @@
     <t>SARMIENTO</t>
   </si>
   <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GARATE</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>ANTEMATE</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>ANGUIANO</t>
+  </si>
+  <si>
+    <t>ELEAZAR RIGOBERTO</t>
+  </si>
+  <si>
+    <t>RAUL ARTURO</t>
+  </si>
+  <si>
+    <t>JOSUE ALEXIS</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>JAFET</t>
+  </si>
+  <si>
+    <t>JUAN ANTONIO</t>
+  </si>
+  <si>
+    <t>ADRIANA</t>
+  </si>
+  <si>
+    <t>AXEL MIGUEL</t>
+  </si>
+  <si>
+    <t>AXEL</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>JOSE ALONSO</t>
+  </si>
+  <si>
+    <t>ROMARIO ALDAIR</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CADEZA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>FLORENCIO</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>OCTAVIANO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>SUAREZ</t>
   </si>
   <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
     <t>TOCOHUA</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GARATE</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ANTEMATE</t>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
+  </si>
+  <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>ANGUIANO</t>
+    <t>DEL ANGEL</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
     <t>BERISTAIN</t>
   </si>
   <si>
-    <t>ELEAZAR RIGOBERTO</t>
-  </si>
-  <si>
-    <t>RAUL ARTURO</t>
-  </si>
-  <si>
-    <t>JOSUE ALEXIS</t>
-  </si>
-  <si>
-    <t>JOSUE</t>
-  </si>
-  <si>
-    <t>JAFET</t>
-  </si>
-  <si>
-    <t>JUAN ANTONIO</t>
-  </si>
-  <si>
-    <t>ADRIANA</t>
-  </si>
-  <si>
-    <t>AXEL MIGUEL</t>
+    <t>JOSE JAZAEL</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>IRVING OTTONIEL</t>
+  </si>
+  <si>
+    <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
+  </si>
+  <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
+    <t>JUAN LUIS</t>
   </si>
   <si>
     <t>MIGUEL ANGEL</t>
   </si>
   <si>
-    <t>AXEL</t>
-  </si>
-  <si>
-    <t>EDUARDO</t>
-  </si>
-  <si>
-    <t>JOSE ALONSO</t>
-  </si>
-  <si>
-    <t>ROMARIO ALDAIR</t>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>OSWALDO ENRIQUE</t>
+  </si>
+  <si>
+    <t>YAEL</t>
+  </si>
+  <si>
+    <t>ARIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>YARITZI</t>
   </si>
   <si>
     <t>YAMILET</t>
   </si>
   <si>
+    <t>MARIA ISABEL</t>
+  </si>
+  <si>
+    <t>JOSUE GILBERTO</t>
+  </si>
+  <si>
     <t>ADOLFO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CADEZA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>FLORENCIO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>OCTAVIANO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>TAPIA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DEL ANGEL</t>
-  </si>
-  <si>
-    <t>MIRON</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>JOSE JAZAEL</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>IRVING OTTONIEL</t>
-  </si>
-  <si>
-    <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
-  </si>
-  <si>
-    <t>JESUS ENRIQUE</t>
-  </si>
-  <si>
-    <t>JUAN LUIS</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>OSWALDO ENRIQUE</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>ARIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>YARITZI</t>
-  </si>
-  <si>
-    <t>MARIA ISABEL</t>
-  </si>
-  <si>
-    <t>JOSUE GILBERTO</t>
   </si>
 </sst>
 </file>
@@ -978,7 +978,7 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>10</v>
@@ -1067,7 +1067,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>10</v>
@@ -1109,7 +1109,7 @@
         <v>10</v>
       </c>
       <c r="AB5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC5">
         <v>10</v>
@@ -1156,7 +1156,7 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
         <v>10</v>
@@ -1245,7 +1245,7 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>10</v>
@@ -1868,7 +1868,7 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>10</v>
@@ -2135,7 +2135,7 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>10</v>
@@ -2292,7 +2292,7 @@
         <v>8</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H19">
         <v>8</v>
@@ -2313,7 +2313,7 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>8</v>
@@ -2355,7 +2355,7 @@
         <v>8</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC19">
         <v>8</v>
@@ -2402,7 +2402,7 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>10</v>
@@ -2580,7 +2580,7 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>10</v>
@@ -2669,7 +2669,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
         <v>10</v>
@@ -2847,7 +2847,7 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>8</v>
@@ -2889,7 +2889,7 @@
         <v>9</v>
       </c>
       <c r="AB25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC25">
         <v>9</v>
@@ -3114,7 +3114,7 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
         <v>10</v>
@@ -3292,7 +3292,7 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
         <v>10</v>
@@ -3449,7 +3449,7 @@
         <v>10</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H32">
         <v>10</v>
@@ -3470,7 +3470,7 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
         <v>10</v>
@@ -3512,7 +3512,7 @@
         <v>10</v>
       </c>
       <c r="AB32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC32">
         <v>10</v>
@@ -3648,7 +3648,7 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>10</v>
@@ -3690,7 +3690,7 @@
         <v>10</v>
       </c>
       <c r="AB34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC34">
         <v>10</v>
@@ -3716,7 +3716,7 @@
         <v>10</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H35">
         <v>10</v>
@@ -3737,7 +3737,7 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>10</v>
@@ -3779,7 +3779,7 @@
         <v>10</v>
       </c>
       <c r="AB35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC35">
         <v>10</v>
@@ -3847,13 +3847,13 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>50</v>
+        <v>59.38</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -3862,10 +3862,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J2">
-        <v>50</v>
+        <v>40.63</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4067,7 +4067,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4102,10 +4102,10 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -4122,10 +4122,10 @@
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4142,10 +4142,10 @@
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -4162,10 +4162,10 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -4182,10 +4182,10 @@
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4205,7 +4205,7 @@
         <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4225,7 +4225,7 @@
         <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -4242,10 +4242,10 @@
         <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -4265,7 +4265,7 @@
         <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -4285,7 +4285,7 @@
         <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -4305,7 +4305,7 @@
         <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
@@ -4325,7 +4325,7 @@
         <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4342,10 +4342,10 @@
         <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -4362,10 +4362,10 @@
         <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -4376,16 +4376,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920102</v>
+        <v>19330051920105</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -4396,16 +4396,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920105</v>
+        <v>19330051920109</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -4425,13 +4425,13 @@
         <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -4445,33 +4445,33 @@
         <v>69</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E19" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920109</v>
+        <v>19330051920112</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -4485,112 +4485,52 @@
         <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920112</v>
+        <v>19330051920116</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D22" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920116</v>
+        <v>19330051920118</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330051920118</v>
-      </c>
-      <c r="B24" t="s">
-        <v>75</v>
-      </c>
-      <c r="C24" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24" t="s">
-        <v>100</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920119</v>
-      </c>
-      <c r="B25" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" t="s">
-        <v>101</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920122</v>
-      </c>
-      <c r="B26" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" t="s">
-        <v>102</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" t="s">
         <v>54</v>
       </c>
     </row>
@@ -4633,10 +4573,10 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -4653,7 +4593,7 @@
         <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -4670,7 +4610,7 @@
         <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -4684,10 +4624,10 @@
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -4704,7 +4644,7 @@
         <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -4721,7 +4661,7 @@
         <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -4735,10 +4675,10 @@
         <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -4755,7 +4695,7 @@
         <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4769,10 +4709,10 @@
         <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4786,10 +4726,10 @@
         <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -4797,16 +4737,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920102</v>
+        <v>19330051920105</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -4814,16 +4754,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920105</v>
+        <v>19330051920116</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -4831,16 +4771,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920116</v>
+        <v>19330051920118</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -4848,64 +4788,64 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920118</v>
+        <v>19330051920085</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920119</v>
+        <v>19330051920084</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920122</v>
+        <v>19330051920088</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920085</v>
+        <v>19330051920090</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="D18" t="s">
         <v>126</v>
@@ -4916,13 +4856,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920084</v>
+        <v>19330051920089</v>
       </c>
       <c r="B19" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
         <v>127</v>
@@ -4933,13 +4873,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920088</v>
+        <v>19330051920097</v>
       </c>
       <c r="B20" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
         <v>128</v>
@@ -4950,13 +4890,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920090</v>
+        <v>19330051920100</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
         <v>129</v>
@@ -4967,13 +4907,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920089</v>
+        <v>19330051920102</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
         <v>130</v>
@@ -4984,13 +4924,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920097</v>
+        <v>19330051920103</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
         <v>131</v>
@@ -5001,13 +4941,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920100</v>
+        <v>19330051920106</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
         <v>132</v>
@@ -5018,13 +4958,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920103</v>
+        <v>19330051920107</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="D25" t="s">
         <v>133</v>
@@ -5035,13 +4975,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920106</v>
+        <v>19330051920110</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
         <v>134</v>
@@ -5052,13 +4992,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920107</v>
+        <v>19330051920001</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s">
-        <v>68</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s">
         <v>135</v>
@@ -5069,16 +5009,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920110</v>
+        <v>19330051920115</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5086,16 +5026,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920001</v>
+        <v>19330051920117</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="D29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5103,16 +5043,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920115</v>
+        <v>19330051920119</v>
       </c>
       <c r="B30" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="D30" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -5120,13 +5060,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920117</v>
+        <v>19330051920120</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
         <v>138</v>
@@ -5137,13 +5077,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920120</v>
+        <v>19330051920121</v>
       </c>
       <c r="B32" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s">
         <v>139</v>
@@ -5154,13 +5094,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>19330051920121</v>
+        <v>19330051920122</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s">
         <v>140</v>
@@ -5176,7 +5116,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5214,10 +5154,10 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -5237,10 +5177,10 @@
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5263,7 +5203,7 @@
         <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -5286,7 +5226,7 @@
         <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5306,10 +5246,10 @@
         <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5329,10 +5269,10 @@
         <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5352,10 +5292,10 @@
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -5375,10 +5315,10 @@
         <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -5392,22 +5332,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920119</v>
+        <v>19330051920085</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5415,16 +5355,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920119</v>
+        <v>19330051920116</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" t="s">
         <v>86</v>
-      </c>
-      <c r="D11" t="s">
-        <v>101</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -5438,22 +5378,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920085</v>
+        <v>19330051920119</v>
       </c>
       <c r="B12" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5461,94 +5401,25 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920102</v>
+        <v>19330051920120</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920116</v>
-      </c>
-      <c r="B14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920120</v>
-      </c>
-      <c r="B15" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" t="s">
-        <v>124</v>
-      </c>
-      <c r="D15" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>19330051920122</v>
-      </c>
-      <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/5BEM - Estadisticos 20211.xlsx
+++ b/grupos/5BEM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="141">
   <si>
     <t>Materia</t>
   </si>
@@ -182,10 +182,10 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
     <t>Ortega Valle Manuel</t>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -1061,7 +1061,7 @@
         <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>10</v>
@@ -1103,7 +1103,7 @@
         <v>7</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>10</v>
@@ -1150,7 +1150,7 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -1192,7 +1192,7 @@
         <v>7</v>
       </c>
       <c r="Z6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA6">
         <v>10</v>
@@ -1239,7 +1239,7 @@
         <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>10</v>
@@ -1328,7 +1328,7 @@
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -1396,7 +1396,7 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F9">
         <v>10</v>
@@ -1459,7 +1459,7 @@
         <v>5</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA9">
         <v>9</v>
@@ -1485,7 +1485,7 @@
         <v>6</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F10">
         <v>10</v>
@@ -1548,7 +1548,7 @@
         <v>7</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA10">
         <v>10</v>
@@ -1595,7 +1595,7 @@
         <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>10</v>
@@ -1684,7 +1684,7 @@
         <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>6</v>
@@ -1773,7 +1773,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>8</v>
@@ -1862,7 +1862,7 @@
         <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
         <v>10</v>
@@ -1930,7 +1930,7 @@
         <v>5</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F15">
         <v>6</v>
@@ -1993,7 +1993,7 @@
         <v>5</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA15">
         <v>6</v>
@@ -2129,7 +2129,7 @@
         <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>10</v>
@@ -2218,7 +2218,7 @@
         <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -2307,7 +2307,7 @@
         <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>8</v>
@@ -2349,7 +2349,7 @@
         <v>8</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA19">
         <v>8</v>
@@ -2396,7 +2396,7 @@
         <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -2574,7 +2574,7 @@
         <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -2663,7 +2663,7 @@
         <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -2731,7 +2731,7 @@
         <v>5</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
         <v>6</v>
@@ -2794,7 +2794,7 @@
         <v>5</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA24">
         <v>6</v>
@@ -2841,7 +2841,7 @@
         <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
         <v>8</v>
@@ -2930,7 +2930,7 @@
         <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>8</v>
@@ -3108,7 +3108,7 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>10</v>
@@ -3197,7 +3197,7 @@
         <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>8</v>
@@ -3239,7 +3239,7 @@
         <v>9</v>
       </c>
       <c r="Z29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA29">
         <v>8</v>
@@ -3286,7 +3286,7 @@
         <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
         <v>10</v>
@@ -3375,7 +3375,7 @@
         <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
         <v>10</v>
@@ -3417,7 +3417,7 @@
         <v>7</v>
       </c>
       <c r="Z31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA31">
         <v>10</v>
@@ -3464,7 +3464,7 @@
         <v>7</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
         <v>10</v>
@@ -3506,7 +3506,7 @@
         <v>7</v>
       </c>
       <c r="Z32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA32">
         <v>10</v>
@@ -3553,7 +3553,7 @@
         <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>8</v>
@@ -3595,7 +3595,7 @@
         <v>9</v>
       </c>
       <c r="Z33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA33">
         <v>8</v>
@@ -3642,7 +3642,7 @@
         <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
         <v>10</v>
@@ -3731,7 +3731,7 @@
         <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M35">
         <v>10</v>
@@ -3838,7 +3838,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -3847,30 +3847,30 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>56.25</v>
+      </c>
+      <c r="G2">
+        <v>43.75</v>
+      </c>
+      <c r="H2">
+        <v>6.7</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>59.38</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="I2">
-        <v>13</v>
-      </c>
-      <c r="J2">
-        <v>40.63</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3879,25 +3879,25 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>62.5</v>
+        <v>59.38</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>12.5</v>
+        <v>40.63</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4067,7 +4067,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4111,24 +4111,24 @@
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920092</v>
+        <v>19330051920091</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>55</v>
@@ -4148,187 +4148,187 @@
         <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920091</v>
+        <v>19330051920093</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920091</v>
+        <v>19330051920093</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920093</v>
+        <v>19330051920094</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920093</v>
+        <v>19330051920095</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
         <v>73</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920094</v>
+        <v>19330051920098</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920095</v>
+        <v>19330051920098</v>
       </c>
       <c r="B10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" t="s">
         <v>68</v>
       </c>
-      <c r="C10" t="s">
-        <v>73</v>
-      </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920098</v>
+        <v>19330051920099</v>
       </c>
       <c r="B11" t="s">
         <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920098</v>
+        <v>19330051920101</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920098</v>
+        <v>19330051920105</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>55</v>
@@ -4336,202 +4336,122 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920099</v>
+        <v>19330051920109</v>
       </c>
       <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s">
         <v>69</v>
       </c>
-      <c r="C14" t="s">
-        <v>79</v>
-      </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920101</v>
+        <v>19330051920109</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920105</v>
+        <v>19330051920112</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920109</v>
+        <v>19330051920112</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920109</v>
+        <v>19330051920116</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920109</v>
+        <v>19330051920118</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19330051920112</v>
-      </c>
-      <c r="B20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" t="s">
-        <v>93</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920112</v>
-      </c>
-      <c r="B21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" t="s">
-        <v>93</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>19330051920116</v>
-      </c>
-      <c r="B22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" t="s">
-        <v>86</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>19330051920118</v>
-      </c>
-      <c r="B23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -4579,55 +4499,55 @@
         <v>84</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920098</v>
+        <v>19330051920093</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920109</v>
+        <v>19330051920098</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920092</v>
+        <v>19330051920109</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -4635,16 +4555,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920093</v>
+        <v>19330051920112</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -4652,19 +4572,19 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920112</v>
+        <v>19330051920092</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5116,7 +5036,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5163,10 +5083,10 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -5186,7 +5106,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -5209,7 +5129,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5232,7 +5152,7 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -5278,7 +5198,7 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -5286,22 +5206,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920118</v>
+        <v>19330051920116</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5309,22 +5229,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920118</v>
+        <v>19330051920116</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -5332,22 +5252,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920085</v>
+        <v>19330051920119</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5355,39 +5275,39 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920116</v>
+        <v>19330051920119</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
         <v>54</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920119</v>
+        <v>19330051920120</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -5396,29 +5316,6 @@
         <v>56</v>
       </c>
       <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920120</v>
-      </c>
-      <c r="B13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C13" t="s">
-        <v>120</v>
-      </c>
-      <c r="D13" t="s">
-        <v>138</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5BEM - Estadisticos 20211.xlsx
+++ b/grupos/5BEM - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="141">
   <si>
     <t>Materia</t>
   </si>
@@ -185,6 +185,9 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
@@ -194,9 +197,6 @@
     <t>Cruz Alejo José Armando</t>
   </si>
   <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
     <t>Aurioles Maldonado Luis Gustavo</t>
   </si>
   <si>
@@ -212,6 +212,18 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CADEZA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>CLEMENTE</t>
   </si>
   <si>
@@ -227,6 +239,9 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>FLORENCIO</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -236,39 +251,123 @@
     <t>HERRERA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>JUAN</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>OCTAVIANO</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TAPIA</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
+    <t>TOCOHUA</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>GALLARDO</t>
   </si>
   <si>
     <t>GARATE</t>
   </si>
   <si>
+    <t>BERNABE</t>
+  </si>
+  <si>
     <t>DIAZ</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>ANTEMATE</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
     <t>AVELINO</t>
   </si>
   <si>
+    <t>DEL ANGEL</t>
+  </si>
+  <si>
+    <t>MIRON</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
     <t>ANGUIANO</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>JOSE JAZAEL</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>IRVING OTTONIEL</t>
+  </si>
+  <si>
+    <t>BRAYAN</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
+  </si>
+  <si>
     <t>ELEAZAR RIGOBERTO</t>
   </si>
   <si>
@@ -284,151 +383,52 @@
     <t>JAFET</t>
   </si>
   <si>
+    <t>JESUS ENRIQUE</t>
+  </si>
+  <si>
     <t>JUAN ANTONIO</t>
   </si>
   <si>
     <t>ADRIANA</t>
   </si>
   <si>
+    <t>JUAN LUIS</t>
+  </si>
+  <si>
     <t>AXEL MIGUEL</t>
   </si>
   <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
     <t>AXEL</t>
   </si>
   <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>OSWALDO ENRIQUE</t>
+  </si>
+  <si>
     <t>EDUARDO</t>
   </si>
   <si>
+    <t>YAEL</t>
+  </si>
+  <si>
     <t>JOSE ALONSO</t>
   </si>
   <si>
+    <t>ARIAN ALEXIS</t>
+  </si>
+  <si>
+    <t>YARITZI</t>
+  </si>
+  <si>
     <t>ROMARIO ALDAIR</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CADEZA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>FLORENCIO</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>OCTAVIANO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>TAPIA</t>
-  </si>
-  <si>
-    <t>TOCOHUA</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>GALLARDO</t>
-  </si>
-  <si>
-    <t>BERNABE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>DEL ANGEL</t>
-  </si>
-  <si>
-    <t>MIRON</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>JOSE JAZAEL</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>IRVING OTTONIEL</t>
-  </si>
-  <si>
-    <t>BRAYAN</t>
-  </si>
-  <si>
-    <t>BRANDON</t>
-  </si>
-  <si>
-    <t>JESUS ENRIQUE</t>
-  </si>
-  <si>
-    <t>JUAN LUIS</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>OSWALDO ENRIQUE</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>ARIAN ALEXIS</t>
-  </si>
-  <si>
-    <t>YARITZI</t>
   </si>
   <si>
     <t>YAMILET</t>
@@ -984,25 +984,25 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -1073,28 +1073,28 @@
         <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -1109,7 +1109,7 @@
         <v>10</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC5">
         <v>10</v>
@@ -1162,25 +1162,25 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1251,25 +1251,25 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1334,31 +1334,31 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1370,13 +1370,13 @@
         <v>9</v>
       </c>
       <c r="Z8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA8">
         <v>10</v>
       </c>
       <c r="AB8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC8">
         <v>10</v>
@@ -1387,7 +1387,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -1402,13 +1402,13 @@
         <v>10</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H9">
         <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1417,46 +1417,46 @@
         <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>8</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
         <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z9">
         <v>5</v>
@@ -1465,7 +1465,7 @@
         <v>9</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC9">
         <v>6</v>
@@ -1491,7 +1491,7 @@
         <v>10</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <v>10</v>
@@ -1506,37 +1506,37 @@
         <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>8</v>
@@ -1548,13 +1548,13 @@
         <v>7</v>
       </c>
       <c r="Z10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA10">
         <v>10</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC10">
         <v>10</v>
@@ -1565,7 +1565,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -1580,13 +1580,13 @@
         <v>10</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H11">
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1601,49 +1601,49 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>7</v>
       </c>
       <c r="Z11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA11">
         <v>10</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC11">
         <v>10</v>
@@ -1669,7 +1669,7 @@
         <v>6</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H12">
         <v>6</v>
@@ -1690,40 +1690,40 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
         <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z12">
         <v>5</v>
@@ -1732,7 +1732,7 @@
         <v>6</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC12">
         <v>6</v>
@@ -1758,7 +1758,7 @@
         <v>8</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H13">
         <v>8</v>
@@ -1779,31 +1779,31 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1812,16 +1812,16 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>8</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC13">
         <v>8</v>
@@ -1874,25 +1874,25 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1921,7 +1921,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C15">
         <v>5</v>
@@ -1936,13 +1936,13 @@
         <v>6</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H15">
         <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -1951,58 +1951,58 @@
         <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
         <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z15">
         <v>5</v>
       </c>
       <c r="AA15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC15">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2025,7 +2025,7 @@
         <v>10</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H16">
         <v>10</v>
@@ -2040,43 +2040,43 @@
         <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>7</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y16">
         <v>7</v>
@@ -2088,7 +2088,7 @@
         <v>10</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC16">
         <v>10</v>
@@ -2141,25 +2141,25 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2171,7 +2171,7 @@
         <v>9</v>
       </c>
       <c r="Z17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA17">
         <v>10</v>
@@ -2203,7 +2203,7 @@
         <v>10</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H18">
         <v>10</v>
@@ -2224,31 +2224,31 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2257,16 +2257,16 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA18">
         <v>10</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC18">
         <v>10</v>
@@ -2319,25 +2319,25 @@
         <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2408,31 +2408,31 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2470,7 +2470,7 @@
         <v>9</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H21">
         <v>9</v>
@@ -2485,55 +2485,55 @@
         <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
         <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21">
         <v>7</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA21">
         <v>9</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC21">
         <v>9</v>
@@ -2586,25 +2586,25 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>10</v>
@@ -2675,25 +2675,25 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2722,7 +2722,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>5</v>
@@ -2737,13 +2737,13 @@
         <v>6</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H24">
         <v>6</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>6</v>
@@ -2752,46 +2752,46 @@
         <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z24">
         <v>5</v>
@@ -2800,7 +2800,7 @@
         <v>6</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC24">
         <v>6</v>
@@ -2853,28 +2853,28 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>8</v>
@@ -2883,7 +2883,7 @@
         <v>8</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA25">
         <v>9</v>
@@ -2900,7 +2900,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C26">
         <v>6</v>
@@ -2915,13 +2915,13 @@
         <v>8</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H26">
         <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
         <v>6</v>
@@ -2936,49 +2936,49 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>6</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA26">
         <v>8</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC26">
         <v>8</v>
@@ -3019,58 +3019,58 @@
         <v>5</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
         <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z27">
         <v>5</v>
       </c>
       <c r="AA27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB27">
         <v>7</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3120,25 +3120,25 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -3147,10 +3147,10 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA28">
         <v>10</v>
@@ -3182,7 +3182,7 @@
         <v>8</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H29">
         <v>8</v>
@@ -3203,31 +3203,31 @@
         <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
         <v>8</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>7</v>
@@ -3236,16 +3236,16 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA29">
         <v>8</v>
       </c>
       <c r="AB29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC29">
         <v>8</v>
@@ -3298,28 +3298,28 @@
         <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -3328,7 +3328,7 @@
         <v>9</v>
       </c>
       <c r="Z30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA30">
         <v>10</v>
@@ -3360,7 +3360,7 @@
         <v>10</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H31">
         <v>10</v>
@@ -3381,49 +3381,49 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
         <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y31">
         <v>7</v>
       </c>
       <c r="Z31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA31">
         <v>10</v>
       </c>
       <c r="AB31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AC31">
         <v>10</v>
@@ -3476,43 +3476,43 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>7</v>
       </c>
       <c r="Z32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA32">
         <v>10</v>
       </c>
       <c r="AB32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC32">
         <v>10</v>
@@ -3559,37 +3559,37 @@
         <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O33">
         <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>7</v>
       </c>
       <c r="X33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y33">
         <v>9</v>
@@ -3654,25 +3654,25 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W34">
         <v>10</v>
@@ -3743,37 +3743,37 @@
         <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y35">
         <v>6</v>
       </c>
       <c r="Z35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA35">
         <v>10</v>
@@ -3847,19 +3847,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>56.25</v>
+        <v>84.38</v>
       </c>
       <c r="G2">
-        <v>43.75</v>
+        <v>15.63</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3870,7 +3870,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -3879,30 +3879,30 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>59.38</v>
+        <v>87.5</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>40.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -3911,19 +3911,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>31.25</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3934,7 +3934,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -3943,19 +3943,19 @@
         <v>32</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>78.13</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>21.88</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -3975,25 +3975,25 @@
         <v>32</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4051,7 +4051,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4067,7 +4067,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4092,366 +4092,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920092</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920091</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920091</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920093</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920093</v>
-      </c>
-      <c r="B6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920094</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920095</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920098</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>19330051920098</v>
-      </c>
-      <c r="B10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920099</v>
-      </c>
-      <c r="B11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920101</v>
-      </c>
-      <c r="B12" t="s">
-        <v>70</v>
-      </c>
-      <c r="C12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920105</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920109</v>
-      </c>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920109</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920112</v>
-      </c>
-      <c r="B16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" t="s">
-        <v>93</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920112</v>
-      </c>
-      <c r="B17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" t="s">
-        <v>68</v>
-      </c>
-      <c r="D17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920116</v>
-      </c>
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" t="s">
-        <v>86</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>19330051920118</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" t="s">
-        <v>94</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4487,87 +4127,87 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920091</v>
+        <v>19330051920085</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920093</v>
+        <v>19330051920084</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920098</v>
+        <v>19330051920088</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920109</v>
+        <v>19330051920090</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920112</v>
+        <v>19330051920089</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4575,149 +4215,149 @@
         <v>19330051920092</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920094</v>
+        <v>19330051920091</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920095</v>
+        <v>19330051920093</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920099</v>
+        <v>19330051920094</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920101</v>
+        <v>19330051920095</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920105</v>
+        <v>19330051920097</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920116</v>
+        <v>19330051920098</v>
       </c>
       <c r="B13" t="s">
         <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920118</v>
+        <v>19330051920099</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920085</v>
+        <v>19330051920100</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4725,16 +4365,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920084</v>
+        <v>19330051920101</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4742,16 +4382,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920088</v>
+        <v>19330051920102</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4759,16 +4399,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920090</v>
+        <v>19330051920105</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4776,16 +4416,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920089</v>
+        <v>19330051920103</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4793,16 +4433,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920097</v>
+        <v>19330051920106</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4810,16 +4450,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920100</v>
+        <v>19330051920107</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4827,16 +4467,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920102</v>
+        <v>19330051920109</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4844,16 +4484,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920103</v>
+        <v>19330051920110</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4861,16 +4501,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920106</v>
+        <v>19330051920112</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="D24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4878,16 +4518,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920107</v>
+        <v>19330051920001</v>
       </c>
       <c r="B25" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4895,16 +4535,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920110</v>
+        <v>19330051920115</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4912,16 +4552,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920001</v>
+        <v>19330051920116</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D27" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -4929,16 +4569,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920115</v>
+        <v>19330051920117</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D28" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4946,13 +4586,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920117</v>
+        <v>19330051920118</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="C29" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s">
         <v>136</v>
@@ -4966,10 +4606,10 @@
         <v>19330051920119</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D30" t="s">
         <v>137</v>
@@ -4983,10 +4623,10 @@
         <v>19330051920120</v>
       </c>
       <c r="B31" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="D31" t="s">
         <v>138</v>
@@ -5000,10 +4640,10 @@
         <v>19330051920121</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
         <v>139</v>
@@ -5017,10 +4657,10 @@
         <v>19330051920122</v>
       </c>
       <c r="B33" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="D33" t="s">
         <v>140</v>
@@ -5036,7 +4676,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5068,22 +4708,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920092</v>
+        <v>19330051920091</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5091,45 +4731,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920092</v>
+        <v>19330051920091</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920095</v>
+        <v>19330051920098</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5137,45 +4777,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920095</v>
+        <v>19330051920098</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920099</v>
+        <v>19330051920109</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5183,45 +4823,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920099</v>
+        <v>19330051920109</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920116</v>
+        <v>19330051920093</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
         <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5229,93 +4869,47 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920116</v>
+        <v>19330051920094</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920119</v>
+        <v>19330051920001</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920119</v>
-      </c>
-      <c r="B11" t="s">
-        <v>106</v>
-      </c>
-      <c r="C11" t="s">
-        <v>119</v>
-      </c>
-      <c r="D11" t="s">
-        <v>137</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920120</v>
-      </c>
-      <c r="B12" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D12" t="s">
-        <v>138</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>
